--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/146.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/146.xlsx
@@ -426,13 +426,13 @@
         <v>-4.230908770755331</v>
       </c>
       <c r="E2">
-        <v>-16.14194240143092</v>
+        <v>-18.99622598304352</v>
       </c>
       <c r="F2">
-        <v>-0.7025675344208664</v>
+        <v>-2.157723274385632</v>
       </c>
       <c r="G2">
-        <v>-7.590131945647395</v>
+        <v>-8.860192946878932</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.991806741713151</v>
       </c>
       <c r="E3">
-        <v>-16.94941913021263</v>
+        <v>-17.21178080032102</v>
       </c>
       <c r="F3">
-        <v>-1.191687007812668</v>
+        <v>-1.874931896948326</v>
       </c>
       <c r="G3">
-        <v>-6.336507803018339</v>
+        <v>-8.012160290993686</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.841623867056167</v>
       </c>
       <c r="E4">
-        <v>-15.91087248671553</v>
+        <v>-17.24674514813424</v>
       </c>
       <c r="F4">
-        <v>-1.952207806853283</v>
+        <v>-1.83239191734496</v>
       </c>
       <c r="G4">
-        <v>-6.357086154090449</v>
+        <v>-7.751693189054907</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.665967959586441</v>
       </c>
       <c r="E5">
-        <v>-17.98461470294405</v>
+        <v>-18.94391305130691</v>
       </c>
       <c r="F5">
-        <v>-1.720235941210323</v>
+        <v>-2.020560543095284</v>
       </c>
       <c r="G5">
-        <v>-6.812352376651022</v>
+        <v>-7.646606542001822</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.436399272582321</v>
       </c>
       <c r="E6">
-        <v>-18.58703760018444</v>
+        <v>-19.56876095183329</v>
       </c>
       <c r="F6">
-        <v>-1.813288936669</v>
+        <v>-1.872956240692649</v>
       </c>
       <c r="G6">
-        <v>-7.393806663531996</v>
+        <v>-7.037638311143966</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.097695228093587</v>
       </c>
       <c r="E7">
-        <v>-19.61191278065238</v>
+        <v>-20.61825744548093</v>
       </c>
       <c r="F7">
-        <v>-1.3917824674285</v>
+        <v>-2.02110975068334</v>
       </c>
       <c r="G7">
-        <v>-6.074706551227234</v>
+        <v>-8.33305809120632</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.617699204381864</v>
       </c>
       <c r="E8">
-        <v>-20.56149302379478</v>
+        <v>-21.50269106154899</v>
       </c>
       <c r="F8">
-        <v>-1.981489766174843</v>
+        <v>-2.276486308924997</v>
       </c>
       <c r="G8">
-        <v>-6.193141317894661</v>
+        <v>-7.721040847906796</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.953928958785303</v>
       </c>
       <c r="E9">
-        <v>-20.60787818305535</v>
+        <v>-22.01938088887616</v>
       </c>
       <c r="F9">
-        <v>-1.765951881436023</v>
+        <v>-2.051586215799737</v>
       </c>
       <c r="G9">
-        <v>-5.463818203956601</v>
+        <v>-7.778919115569874</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.081778435257805</v>
       </c>
       <c r="E10">
-        <v>-21.16517936528331</v>
+        <v>-22.36486722786935</v>
       </c>
       <c r="F10">
-        <v>-1.306526065964972</v>
+        <v>-1.926682493703419</v>
       </c>
       <c r="G10">
-        <v>-6.006357028023441</v>
+        <v>-7.480367497747319</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.985527672601338</v>
       </c>
       <c r="E11">
-        <v>-24.24144421427791</v>
+        <v>-23.13702638786524</v>
       </c>
       <c r="F11">
-        <v>-1.582466016613724</v>
+        <v>-1.886968903678405</v>
       </c>
       <c r="G11">
-        <v>-5.692560347992544</v>
+        <v>-7.717654159820121</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.660041212186899</v>
       </c>
       <c r="E12">
-        <v>-23.27525352847537</v>
+        <v>-23.66850168282745</v>
       </c>
       <c r="F12">
-        <v>-1.47163045811915</v>
+        <v>-1.90417989320637</v>
       </c>
       <c r="G12">
-        <v>-5.284873285922375</v>
+        <v>-6.344903346505931</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.109007417774492</v>
       </c>
       <c r="E13">
-        <v>-23.96013088044742</v>
+        <v>-25.18371097189792</v>
       </c>
       <c r="F13">
-        <v>-1.725470394828614</v>
+        <v>-1.231673130713203</v>
       </c>
       <c r="G13">
-        <v>-4.869482584382323</v>
+        <v>-5.644246246392419</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.353994166401446</v>
       </c>
       <c r="E14">
-        <v>-23.18202583407946</v>
+        <v>-25.08092819734583</v>
       </c>
       <c r="F14">
-        <v>-1.154013686700749</v>
+        <v>-1.32749867186905</v>
       </c>
       <c r="G14">
-        <v>-3.416931070844</v>
+        <v>-5.432990403894907</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.42189307651373</v>
       </c>
       <c r="E15">
-        <v>-25.88848643865968</v>
+        <v>-26.8684210430755</v>
       </c>
       <c r="F15">
-        <v>-1.103040926936885</v>
+        <v>-1.381501599592355</v>
       </c>
       <c r="G15">
-        <v>-5.024498879258696</v>
+        <v>-4.458961695330538</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.346843416117915</v>
       </c>
       <c r="E16">
-        <v>-27.33007632578745</v>
+        <v>-26.58287358604784</v>
       </c>
       <c r="F16">
-        <v>-1.257866107989724</v>
+        <v>-1.393745698173135</v>
       </c>
       <c r="G16">
-        <v>-3.889852432765507</v>
+        <v>-4.772238619711771</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.17484491121247</v>
       </c>
       <c r="E17">
-        <v>-27.75616497364316</v>
+        <v>-28.69964083382323</v>
       </c>
       <c r="F17">
-        <v>-0.4357520507139513</v>
+        <v>-0.7739678343377671</v>
       </c>
       <c r="G17">
-        <v>-2.301224255380982</v>
+        <v>-4.522461269319299</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.948967496639151</v>
       </c>
       <c r="E18">
-        <v>-29.24890850316158</v>
+        <v>-29.0238025887143</v>
       </c>
       <c r="F18">
-        <v>-0.9518738163348085</v>
+        <v>-1.454368938179614</v>
       </c>
       <c r="G18">
-        <v>-1.5947108002085</v>
+        <v>-4.150971712175522</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.708874390509014</v>
       </c>
       <c r="E19">
-        <v>-29.69835728418586</v>
+        <v>-29.69845917485103</v>
       </c>
       <c r="F19">
-        <v>-0.9793416510442373</v>
+        <v>-1.015222385096498</v>
       </c>
       <c r="G19">
-        <v>-2.123894883569921</v>
+        <v>-3.964021895027339</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4970649254794862</v>
       </c>
       <c r="E20">
-        <v>-30.30375765308629</v>
+        <v>-30.57198822550862</v>
       </c>
       <c r="F20">
-        <v>-0.2656111847507524</v>
+        <v>-0.910063628413309</v>
       </c>
       <c r="G20">
-        <v>-1.602821636779715</v>
+        <v>-3.633129557831645</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.6472823713101371</v>
       </c>
       <c r="E21">
-        <v>-31.28328695907842</v>
+        <v>-31.50638449530331</v>
       </c>
       <c r="F21">
-        <v>-0.5209703472769505</v>
+        <v>-0.3522990050863179</v>
       </c>
       <c r="G21">
-        <v>-1.542477012689879</v>
+        <v>-3.65768056355088</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.692549308013904</v>
       </c>
       <c r="E22">
-        <v>-28.96111492302612</v>
+        <v>-32.49142721839978</v>
       </c>
       <c r="F22">
-        <v>0.2028488056152296</v>
+        <v>0.04376415937719573</v>
       </c>
       <c r="G22">
-        <v>-1.862960994710105</v>
+        <v>-2.837628638563553</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.611424693816736</v>
       </c>
       <c r="E23">
-        <v>-30.80422195804398</v>
+        <v>-32.81815661805319</v>
       </c>
       <c r="F23">
-        <v>-0.8327885468757543</v>
+        <v>0.2531099977800896</v>
       </c>
       <c r="G23">
-        <v>0.4002669788483275</v>
+        <v>-4.000437895959323</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.372018473223386</v>
       </c>
       <c r="E24">
-        <v>-31.99015458083172</v>
+        <v>-33.60385591533202</v>
       </c>
       <c r="F24">
-        <v>0.1788659125693783</v>
+        <v>0.3513916482852369</v>
       </c>
       <c r="G24">
-        <v>-0.02644247789049288</v>
+        <v>-2.830716219477555</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.956419722253155</v>
       </c>
       <c r="E25">
-        <v>-33.24262180797716</v>
+        <v>-32.31531486424148</v>
       </c>
       <c r="F25">
-        <v>0.3724313519489416</v>
+        <v>0.243403188554085</v>
       </c>
       <c r="G25">
-        <v>-2.274653816882791</v>
+        <v>-2.785418024863707</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.35723647854749</v>
       </c>
       <c r="E26">
-        <v>-32.83862079209386</v>
+        <v>-33.40539554194586</v>
       </c>
       <c r="F26">
-        <v>1.100978825976301</v>
+        <v>0.4243592193282342</v>
       </c>
       <c r="G26">
-        <v>-1.127000236965806</v>
+        <v>-2.886131441259415</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.573954906265421</v>
       </c>
       <c r="E27">
-        <v>-34.44645775275422</v>
+        <v>-33.72016297750802</v>
       </c>
       <c r="F27">
-        <v>1.069023725045907</v>
+        <v>0.1619456799997956</v>
       </c>
       <c r="G27">
-        <v>-1.660683351715097</v>
+        <v>-3.061123567919751</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.616990624852835</v>
       </c>
       <c r="E28">
-        <v>-33.94074721065865</v>
+        <v>-33.68012673880621</v>
       </c>
       <c r="F28">
-        <v>0.9505290815450493</v>
+        <v>0.3411745647391078</v>
       </c>
       <c r="G28">
-        <v>0.2661302946881375</v>
+        <v>-3.101621471501656</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.502671908040258</v>
       </c>
       <c r="E29">
-        <v>-35.18906861985006</v>
+        <v>-33.95909205886372</v>
       </c>
       <c r="F29">
-        <v>1.050552788698284</v>
+        <v>-0.123873380294743</v>
       </c>
       <c r="G29">
-        <v>-0.8929976360679617</v>
+        <v>-3.548651056760523</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.249304370723974</v>
       </c>
       <c r="E30">
-        <v>-33.67345856082991</v>
+        <v>-33.97516361311694</v>
       </c>
       <c r="F30">
-        <v>1.043665742111409</v>
+        <v>0.3961210029342018</v>
       </c>
       <c r="G30">
-        <v>-1.49541760784914</v>
+        <v>-2.922030997087272</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.871686362223454</v>
       </c>
       <c r="E31">
-        <v>-34.21814794294651</v>
+        <v>-33.36487928499924</v>
       </c>
       <c r="F31">
-        <v>1.018995304121234</v>
+        <v>0.4751961268380399</v>
       </c>
       <c r="G31">
-        <v>-2.717485630397863</v>
+        <v>-3.276947963261458</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.384544008234527</v>
       </c>
       <c r="E32">
-        <v>-32.02719296974045</v>
+        <v>-32.50641193889116</v>
       </c>
       <c r="F32">
-        <v>0.2777390174001245</v>
+        <v>0.03636601010279334</v>
       </c>
       <c r="G32">
-        <v>-0.489405718829872</v>
+        <v>-3.156914203098563</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.801760262028543</v>
       </c>
       <c r="E33">
-        <v>-33.31280409814804</v>
+        <v>-33.2917036735093</v>
       </c>
       <c r="F33">
-        <v>1.038297921341268</v>
+        <v>-0.01019155140415007</v>
       </c>
       <c r="G33">
-        <v>-1.443216925785912</v>
+        <v>-3.184540705623781</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.138857577361149</v>
       </c>
       <c r="E34">
-        <v>-32.46859918092711</v>
+        <v>-32.13052142541048</v>
       </c>
       <c r="F34">
-        <v>0.1892395575546365</v>
+        <v>0.3692321970393299</v>
       </c>
       <c r="G34">
-        <v>-1.757592951286182</v>
+        <v>-2.911950385920191</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.411023764631204</v>
       </c>
       <c r="E35">
-        <v>-33.53566162525051</v>
+        <v>-31.44735130813932</v>
       </c>
       <c r="F35">
-        <v>0.5467794959509591</v>
+        <v>0.4846925307437334</v>
       </c>
       <c r="G35">
-        <v>-3.427372531474862</v>
+        <v>-3.122047537478959</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.6358546841083117</v>
       </c>
       <c r="E36">
-        <v>-31.9751449537333</v>
+        <v>-32.23631337094066</v>
       </c>
       <c r="F36">
-        <v>0.4954347992232374</v>
+        <v>0.325205297947939</v>
       </c>
       <c r="G36">
-        <v>-2.787089850361039</v>
+        <v>-3.566349233213467</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.1633224525569978</v>
       </c>
       <c r="E37">
-        <v>-31.16467716786952</v>
+        <v>-31.30371716956403</v>
       </c>
       <c r="F37">
-        <v>0.4447403709067132</v>
+        <v>-0.04980325223861963</v>
       </c>
       <c r="G37">
-        <v>-2.607813877772887</v>
+        <v>-3.570153050038089</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.9697281439873475</v>
       </c>
       <c r="E38">
-        <v>-32.8043447723298</v>
+        <v>-31.41377040913544</v>
       </c>
       <c r="F38">
-        <v>0.08528027687070135</v>
+        <v>0.02389328211884119</v>
       </c>
       <c r="G38">
-        <v>-1.551756471836457</v>
+        <v>-4.071316675955118</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.768490339865973</v>
       </c>
       <c r="E39">
-        <v>-32.48648665325741</v>
+        <v>-29.87917245860113</v>
       </c>
       <c r="F39">
-        <v>0.5095195301730373</v>
+        <v>0.1383090445283145</v>
       </c>
       <c r="G39">
-        <v>-3.032040425357254</v>
+        <v>-3.857332943933247</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.541501172505566</v>
       </c>
       <c r="E40">
-        <v>-30.6981424544143</v>
+        <v>-29.65708250784295</v>
       </c>
       <c r="F40">
-        <v>0.9261883337811887</v>
+        <v>-0.3927299612821561</v>
       </c>
       <c r="G40">
-        <v>-0.2052748373763831</v>
+        <v>-3.68025517358317</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.274840857043201</v>
       </c>
       <c r="E41">
-        <v>-29.32651296223103</v>
+        <v>-28.41784295327392</v>
       </c>
       <c r="F41">
-        <v>0.5962338582654924</v>
+        <v>-0.1035121095339312</v>
       </c>
       <c r="G41">
-        <v>-2.080907449742485</v>
+        <v>-4.506127037628535</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.961411117375746</v>
       </c>
       <c r="E42">
-        <v>-28.92758610147332</v>
+        <v>-28.51236579123602</v>
       </c>
       <c r="F42">
-        <v>1.264016441460494</v>
+        <v>-0.07689500814717747</v>
       </c>
       <c r="G42">
-        <v>-1.930357080798588</v>
+        <v>-4.033291749891049</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.593929789612848</v>
       </c>
       <c r="E43">
-        <v>-27.74137950600812</v>
+        <v>-29.35143315469524</v>
       </c>
       <c r="F43">
-        <v>0.08411890577197645</v>
+        <v>0.0337616229883917</v>
       </c>
       <c r="G43">
-        <v>-0.9722322330048783</v>
+        <v>-4.046427994590878</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.164693322835163</v>
       </c>
       <c r="E44">
-        <v>-27.46408745709644</v>
+        <v>-28.9157622558393</v>
       </c>
       <c r="F44">
-        <v>0.5753797089000149</v>
+        <v>0.4996636148145288</v>
       </c>
       <c r="G44">
-        <v>-0.7753739530576564</v>
+        <v>-3.031633228255923</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.675907035946869</v>
       </c>
       <c r="E45">
-        <v>-25.98828042036671</v>
+        <v>-26.88030828734563</v>
       </c>
       <c r="F45">
-        <v>0.9560195006908044</v>
+        <v>0.05702300802640461</v>
       </c>
       <c r="G45">
-        <v>-1.731774006625406</v>
+        <v>-4.404824344126837</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.129881395383468</v>
       </c>
       <c r="E46">
-        <v>-25.42170492337104</v>
+        <v>-27.32637656252318</v>
       </c>
       <c r="F46">
-        <v>1.682819119498257</v>
+        <v>0.4632668078703241</v>
       </c>
       <c r="G46">
-        <v>-2.606430069737471</v>
+        <v>-3.545469622497283</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.523911833751768</v>
       </c>
       <c r="E47">
-        <v>-26.35503700177392</v>
+        <v>-25.07715145002343</v>
       </c>
       <c r="F47">
-        <v>0.7560913712903382</v>
+        <v>0.324750524243802</v>
       </c>
       <c r="G47">
-        <v>-2.845213098394024</v>
+        <v>-3.675875321834714</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.86798686149185</v>
       </c>
       <c r="E48">
-        <v>-23.49289651775801</v>
+        <v>-25.6772602970459</v>
       </c>
       <c r="F48">
-        <v>1.310895409519724</v>
+        <v>0.5693433956358148</v>
       </c>
       <c r="G48">
-        <v>-2.457703811385713</v>
+        <v>-4.109288633290559</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.170560310322663</v>
       </c>
       <c r="E49">
-        <v>-23.57261577418904</v>
+        <v>-24.09897389352259</v>
       </c>
       <c r="F49">
-        <v>0.514115312523769</v>
+        <v>0.7702067518340417</v>
       </c>
       <c r="G49">
-        <v>-1.68696577275137</v>
+        <v>-3.618530052003459</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.432828573248903</v>
       </c>
       <c r="E50">
-        <v>-21.7385566302385</v>
+        <v>-22.9966663359975</v>
       </c>
       <c r="F50">
-        <v>1.425362530708171</v>
+        <v>0.2147781245829453</v>
       </c>
       <c r="G50">
-        <v>-2.372576443388894</v>
+        <v>-3.310967129223009</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.665293235608659</v>
       </c>
       <c r="E51">
-        <v>-22.14012811981668</v>
+        <v>-24.2773323707887</v>
       </c>
       <c r="F51">
-        <v>1.193461076294449</v>
+        <v>0.3955784222853682</v>
       </c>
       <c r="G51">
-        <v>-3.292477732386179</v>
+        <v>-3.513751285685526</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.878309679790476</v>
       </c>
       <c r="E52">
-        <v>-22.43038971828633</v>
+        <v>-23.36097301296656</v>
       </c>
       <c r="F52">
-        <v>0.8580501446965125</v>
+        <v>0.7993702546170012</v>
       </c>
       <c r="G52">
-        <v>-2.277305563859748</v>
+        <v>-2.503157601639907</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.075088693718298</v>
       </c>
       <c r="E53">
-        <v>-23.01386095180462</v>
+        <v>-21.14820211622855</v>
       </c>
       <c r="F53">
-        <v>1.251571049600835</v>
+        <v>0.4102951975635042</v>
       </c>
       <c r="G53">
-        <v>-1.426445702083964</v>
+        <v>-3.242266688192053</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.25950055669006</v>
       </c>
       <c r="E54">
-        <v>-21.2170666204632</v>
+        <v>-20.82632724071136</v>
       </c>
       <c r="F54">
-        <v>1.943817807302714</v>
+        <v>0.2331413731682047</v>
       </c>
       <c r="G54">
-        <v>-2.671455805219836</v>
+        <v>-4.142245114134004</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.44198509735781</v>
       </c>
       <c r="E55">
-        <v>-20.35333718755821</v>
+        <v>-20.37462101539426</v>
       </c>
       <c r="F55">
-        <v>1.141717934845981</v>
+        <v>0.6254106149268965</v>
       </c>
       <c r="G55">
-        <v>-2.935855835259269</v>
+        <v>-3.818688945853334</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.624587691831545</v>
       </c>
       <c r="E56">
-        <v>-18.7100490681288</v>
+        <v>-21.2471175739781</v>
       </c>
       <c r="F56">
-        <v>1.475256756113591</v>
+        <v>0.8553596073722197</v>
       </c>
       <c r="G56">
-        <v>-2.642445494659203</v>
+        <v>-3.214881855491202</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.798581631287178</v>
       </c>
       <c r="E57">
-        <v>-17.56064085244992</v>
+        <v>-19.71628957805517</v>
       </c>
       <c r="F57">
-        <v>1.72825507154181</v>
+        <v>0.9558538272102446</v>
       </c>
       <c r="G57">
-        <v>-2.755960790655272</v>
+        <v>-3.327864153655449</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.969591851476613</v>
       </c>
       <c r="E58">
-        <v>-18.82857734680556</v>
+        <v>-19.53453021680931</v>
       </c>
       <c r="F58">
-        <v>1.884110741643731</v>
+        <v>0.9818711905973715</v>
       </c>
       <c r="G58">
-        <v>-3.342208747477111</v>
+        <v>-4.392595188904769</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.132581622833104</v>
       </c>
       <c r="E59">
-        <v>-17.27262990556209</v>
+        <v>-20.02159023870429</v>
       </c>
       <c r="F59">
-        <v>1.172930818583466</v>
+        <v>0.9117581736244212</v>
       </c>
       <c r="G59">
-        <v>-3.944191727247105</v>
+        <v>-4.052393597652644</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.272684446020381</v>
       </c>
       <c r="E60">
-        <v>-15.88472960626925</v>
+        <v>-17.69570258972869</v>
       </c>
       <c r="F60">
-        <v>2.222059790963846</v>
+        <v>0.4852583056798455</v>
       </c>
       <c r="G60">
-        <v>-2.698036175354645</v>
+        <v>-5.294728779992785</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.386857178112784</v>
       </c>
       <c r="E61">
-        <v>-18.18652124505004</v>
+        <v>-17.7467747195872</v>
       </c>
       <c r="F61">
-        <v>1.926259731832976</v>
+        <v>0.8931099666525988</v>
       </c>
       <c r="G61">
-        <v>-2.84913609485806</v>
+        <v>-4.751004780622885</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.468653016339308</v>
       </c>
       <c r="E62">
-        <v>-18.73920338379018</v>
+        <v>-17.62818757074833</v>
       </c>
       <c r="F62">
-        <v>1.644841787549511</v>
+        <v>1.022780943152028</v>
       </c>
       <c r="G62">
-        <v>-3.510195759776348</v>
+        <v>-5.49643700915504</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.504454929571478</v>
       </c>
       <c r="E63">
-        <v>-15.38508495510695</v>
+        <v>-17.962742173487</v>
       </c>
       <c r="F63">
-        <v>1.286904232799845</v>
+        <v>0.9150020603737842</v>
       </c>
       <c r="G63">
-        <v>-4.442504973454821</v>
+        <v>-6.138050529575649</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.484215896332017</v>
       </c>
       <c r="E64">
-        <v>-17.11096791196226</v>
+        <v>-17.93913071001101</v>
       </c>
       <c r="F64">
-        <v>1.455433924164598</v>
+        <v>0.5242230515727285</v>
       </c>
       <c r="G64">
-        <v>-3.862831760073976</v>
+        <v>-5.347677645347889</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.40503398341256</v>
       </c>
       <c r="E65">
-        <v>-15.98667461312993</v>
+        <v>-16.9842929085457</v>
       </c>
       <c r="F65">
-        <v>1.485004983709735</v>
+        <v>0.09612194943854128</v>
       </c>
       <c r="G65">
-        <v>-2.556384552820309</v>
+        <v>-5.108129880671765</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.257460292383895</v>
       </c>
       <c r="E66">
-        <v>-16.86638955928199</v>
+        <v>-17.61147297318602</v>
       </c>
       <c r="F66">
-        <v>1.526343830579042</v>
+        <v>0.3362333531814088</v>
       </c>
       <c r="G66">
-        <v>-4.362664546684218</v>
+        <v>-5.312820911364902</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.02924486106561</v>
       </c>
       <c r="E67">
-        <v>-15.27431395240533</v>
+        <v>-16.90265357913542</v>
       </c>
       <c r="F67">
-        <v>1.485231956378102</v>
+        <v>0.4074215910431927</v>
       </c>
       <c r="G67">
-        <v>-3.652602186693638</v>
+        <v>-5.567954724439915</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.721939217845328</v>
       </c>
       <c r="E68">
-        <v>-14.29361856435622</v>
+        <v>-16.41385009474748</v>
       </c>
       <c r="F68">
-        <v>1.720299431005323</v>
+        <v>0.2550185562761397</v>
       </c>
       <c r="G68">
-        <v>-3.764091428819674</v>
+        <v>-5.141695501894436</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.329782587850708</v>
       </c>
       <c r="E69">
-        <v>-16.2168478899918</v>
+        <v>-16.73642688373586</v>
       </c>
       <c r="F69">
-        <v>1.519085675395712</v>
+        <v>0.3683044255481944</v>
       </c>
       <c r="G69">
-        <v>-3.992293953932715</v>
+        <v>-5.478596479243907</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.844929419561044</v>
       </c>
       <c r="E70">
-        <v>-16.06324205165162</v>
+        <v>-16.44041412327648</v>
       </c>
       <c r="F70">
-        <v>1.498002068259659</v>
+        <v>-0.01007226649814694</v>
       </c>
       <c r="G70">
-        <v>-4.258243319284526</v>
+        <v>-6.019920333097835</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.272758214495874</v>
       </c>
       <c r="E71">
-        <v>-12.66645634086812</v>
+        <v>-16.77591517708275</v>
       </c>
       <c r="F71">
-        <v>0.8618258433184727</v>
+        <v>-0.2452871905230666</v>
       </c>
       <c r="G71">
-        <v>-3.581326141233129</v>
+        <v>-5.556318156869377</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.615936180297348</v>
       </c>
       <c r="E72">
-        <v>-14.3158035585198</v>
+        <v>-16.06059742283114</v>
       </c>
       <c r="F72">
-        <v>0.6166249502528051</v>
+        <v>0.1244885627800076</v>
       </c>
       <c r="G72">
-        <v>-2.554808733143616</v>
+        <v>-5.086459049571696</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.875750851991159</v>
       </c>
       <c r="E73">
-        <v>-13.82414260703302</v>
+        <v>-17.02018106505649</v>
       </c>
       <c r="F73">
-        <v>0.9206283317735984</v>
+        <v>0.1276960013636472</v>
       </c>
       <c r="G73">
-        <v>-3.8419190439024</v>
+        <v>-5.730115176590036</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.063140187561303</v>
       </c>
       <c r="E74">
-        <v>-16.44247910742397</v>
+        <v>-16.22952761721327</v>
       </c>
       <c r="F74">
-        <v>0.9459266722550953</v>
+        <v>-0.4530798400457113</v>
       </c>
       <c r="G74">
-        <v>-4.590234757599259</v>
+        <v>-4.789380624514117</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.190810359808279</v>
       </c>
       <c r="E75">
-        <v>-17.13314837765183</v>
+        <v>-15.89194346536347</v>
       </c>
       <c r="F75">
-        <v>0.3246386946444241</v>
+        <v>0.0927372402307025</v>
       </c>
       <c r="G75">
-        <v>-2.658392392521872</v>
+        <v>-4.279586406376208</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.269271490238518</v>
       </c>
       <c r="E76">
-        <v>-14.15484347839116</v>
+        <v>-16.58782953764817</v>
       </c>
       <c r="F76">
-        <v>1.034262115354829</v>
+        <v>-0.3874946792964633</v>
       </c>
       <c r="G76">
-        <v>-4.328291152349966</v>
+        <v>-4.507987564221605</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.312860910516032</v>
       </c>
       <c r="E77">
-        <v>-15.15565887645635</v>
+        <v>-15.69476012164748</v>
       </c>
       <c r="F77">
-        <v>-0.1102864981540255</v>
+        <v>-0.6395933877252424</v>
       </c>
       <c r="G77">
-        <v>-2.011548210149214</v>
+        <v>-5.158092633950446</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.345438627442129</v>
       </c>
       <c r="E78">
-        <v>-13.83622910415949</v>
+        <v>-16.77528119072167</v>
       </c>
       <c r="F78">
-        <v>0.1028143296857585</v>
+        <v>-1.093243825663975</v>
       </c>
       <c r="G78">
-        <v>-4.321127131802982</v>
+        <v>-4.180558057659989</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.3828464554857023</v>
       </c>
       <c r="E79">
-        <v>-17.35192348543639</v>
+        <v>-17.25424430109095</v>
       </c>
       <c r="F79">
-        <v>0.4504006053700422</v>
+        <v>-0.7855939708360581</v>
       </c>
       <c r="G79">
-        <v>-2.295576464690986</v>
+        <v>-3.358105987156691</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5590895804344139</v>
       </c>
       <c r="E80">
-        <v>-15.56067200628036</v>
+        <v>-17.4943258790816</v>
       </c>
       <c r="F80">
-        <v>-0.131884521447217</v>
+        <v>-0.730817347958538</v>
       </c>
       <c r="G80">
-        <v>-2.022092297691793</v>
+        <v>-4.245305707317055</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.457317605946024</v>
       </c>
       <c r="E81">
-        <v>-16.87100860276982</v>
+        <v>-19.01270509995744</v>
       </c>
       <c r="F81">
-        <v>0.08659241083673577</v>
+        <v>-0.8398478938824118</v>
       </c>
       <c r="G81">
-        <v>-2.112867456378609</v>
+        <v>-3.351819261177615</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.298435773136329</v>
       </c>
       <c r="E82">
-        <v>-16.00810335213422</v>
+        <v>-19.86033580776516</v>
       </c>
       <c r="F82">
-        <v>-0.06186345325597763</v>
+        <v>-1.097351699614458</v>
       </c>
       <c r="G82">
-        <v>-2.27983813119729</v>
+        <v>-2.807131893055787</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.072800074771876</v>
       </c>
       <c r="E83">
-        <v>-17.38584628422785</v>
+        <v>-20.51714114936366</v>
       </c>
       <c r="F83">
-        <v>-1.181350639360536</v>
+        <v>-1.468680641797781</v>
       </c>
       <c r="G83">
-        <v>-2.185080386226731</v>
+        <v>-2.829252958349197</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.766273627213181</v>
       </c>
       <c r="E84">
-        <v>-19.16289646889583</v>
+        <v>-20.00864785999037</v>
       </c>
       <c r="F84">
-        <v>-0.5840215321410348</v>
+        <v>-1.584789587178576</v>
       </c>
       <c r="G84">
-        <v>-2.207241178066612</v>
+        <v>-3.225853003408346</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.371339855502424</v>
       </c>
       <c r="E85">
-        <v>-19.92123472622031</v>
+        <v>-20.38839210485158</v>
       </c>
       <c r="F85">
-        <v>-0.5617077994118245</v>
+        <v>-1.42100229919485</v>
       </c>
       <c r="G85">
-        <v>-1.170663022083254</v>
+        <v>-3.353828762319953</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.883650827378271</v>
       </c>
       <c r="E86">
-        <v>-21.01420909881559</v>
+        <v>-22.58368762039399</v>
       </c>
       <c r="F86">
-        <v>-0.8553060579860533</v>
+        <v>-1.639010375528818</v>
       </c>
       <c r="G86">
-        <v>-3.404768126532718</v>
+        <v>-2.56174101550285</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.298251522704978</v>
       </c>
       <c r="E87">
-        <v>-20.83195160542889</v>
+        <v>-23.46535433884336</v>
       </c>
       <c r="F87">
-        <v>-1.54930067090784</v>
+        <v>-1.491908063772279</v>
       </c>
       <c r="G87">
-        <v>-1.270952688649935</v>
+        <v>-2.146876690703542</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.610501749676589</v>
       </c>
       <c r="E88">
-        <v>-22.36633445344783</v>
+        <v>-22.97007513662446</v>
       </c>
       <c r="F88">
-        <v>-1.816208103396466</v>
+        <v>-1.46066453044089</v>
       </c>
       <c r="G88">
-        <v>-1.871124800009948</v>
+        <v>-3.506345595314176</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.820963674435603</v>
       </c>
       <c r="E89">
-        <v>-23.43629512113614</v>
+        <v>-24.77299649329825</v>
       </c>
       <c r="F89">
-        <v>-1.830392238434602</v>
+        <v>-2.101472985898531</v>
       </c>
       <c r="G89">
-        <v>-2.133078336895859</v>
+        <v>-2.577585286453802</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.928468492849011</v>
       </c>
       <c r="E90">
-        <v>-24.4490792760036</v>
+        <v>-25.20142636221593</v>
       </c>
       <c r="F90">
-        <v>-2.608776780516588</v>
+        <v>-2.520448792723479</v>
       </c>
       <c r="G90">
-        <v>-2.831613377318698</v>
+        <v>-2.834457135936931</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.932021407691786</v>
       </c>
       <c r="E91">
-        <v>-27.78851639195396</v>
+        <v>-26.05492597233759</v>
       </c>
       <c r="F91">
-        <v>-2.244889062712613</v>
+        <v>-2.500583714036944</v>
       </c>
       <c r="G91">
-        <v>-1.92376247408436</v>
+        <v>-3.131442865719411</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.833749607279048</v>
       </c>
       <c r="E92">
-        <v>-27.58094925733838</v>
+        <v>-28.47307222227147</v>
       </c>
       <c r="F92">
-        <v>-2.7308085528274</v>
+        <v>-2.652942845331649</v>
       </c>
       <c r="G92">
-        <v>-2.625773587323433</v>
+        <v>-2.879675877457837</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.634438026040007</v>
       </c>
       <c r="E93">
-        <v>-31.68017374229568</v>
+        <v>-29.28291734295919</v>
       </c>
       <c r="F93">
-        <v>-2.426559974555378</v>
+        <v>-2.686600241274796</v>
       </c>
       <c r="G93">
-        <v>-2.327076305497151</v>
+        <v>-3.977989086657524</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.335253408637326</v>
       </c>
       <c r="E94">
-        <v>-32.75260016408116</v>
+        <v>-31.99726428502376</v>
       </c>
       <c r="F94">
-        <v>-2.563517270729831</v>
+        <v>-3.01737065868225</v>
       </c>
       <c r="G94">
-        <v>-2.332369867814446</v>
+        <v>-3.222433209866279</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.9446825307186</v>
       </c>
       <c r="E95">
-        <v>-33.12236138799246</v>
+        <v>-34.06490438252695</v>
       </c>
       <c r="F95">
-        <v>-2.118432980103448</v>
+        <v>-3.028711836793978</v>
       </c>
       <c r="G95">
-        <v>-2.655432764809764</v>
+        <v>-3.837592160882572</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.464486457217824</v>
       </c>
       <c r="E96">
-        <v>-35.85832952920666</v>
+        <v>-34.63327315522965</v>
       </c>
       <c r="F96">
-        <v>-3.281472410777594</v>
+        <v>-3.063977922233361</v>
       </c>
       <c r="G96">
-        <v>-2.597779614243356</v>
+        <v>-3.585219342787312</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.908832699601044</v>
       </c>
       <c r="E97">
-        <v>-36.60811576336765</v>
+        <v>-36.58840105177526</v>
       </c>
       <c r="F97">
-        <v>-4.019604095655343</v>
+        <v>-3.551835792070699</v>
       </c>
       <c r="G97">
-        <v>-3.450284817152158</v>
+        <v>-4.062331855361537</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.279978858014753</v>
       </c>
       <c r="E98">
-        <v>-38.75767142719558</v>
+        <v>-40.26533401433228</v>
       </c>
       <c r="F98">
-        <v>-3.703276263915699</v>
+        <v>-3.990098477135028</v>
       </c>
       <c r="G98">
-        <v>-3.27348513262738</v>
+        <v>-4.015308866521728</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.61605264782445</v>
       </c>
       <c r="E99">
-        <v>-40.52981727451326</v>
+        <v>-41.67308940791174</v>
       </c>
       <c r="F99">
-        <v>-4.435036146731115</v>
+        <v>-4.028778264641348</v>
       </c>
       <c r="G99">
-        <v>-4.298320783582944</v>
+        <v>-4.72386823883748</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.900002663396005</v>
       </c>
       <c r="E100">
-        <v>-43.62368430197566</v>
+        <v>-43.50408277495909</v>
       </c>
       <c r="F100">
-        <v>-3.840583131134134</v>
+        <v>-4.388394091749086</v>
       </c>
       <c r="G100">
-        <v>-4.245613588052207</v>
+        <v>-4.919763150032773</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.209155233233568</v>
       </c>
       <c r="E101">
-        <v>-45.20550970793597</v>
+        <v>-45.02313673846207</v>
       </c>
       <c r="F101">
-        <v>-3.936306783099436</v>
+        <v>-4.470357732786487</v>
       </c>
       <c r="G101">
-        <v>-4.113049413023171</v>
+        <v>-5.145386760170723</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4778434891225495</v>
       </c>
       <c r="E102">
-        <v>-46.7106521992874</v>
+        <v>-47.50543787966261</v>
       </c>
       <c r="F102">
-        <v>-4.31835645620979</v>
+        <v>-4.785084330336519</v>
       </c>
       <c r="G102">
-        <v>-5.031858221992496</v>
+        <v>-4.931552002698118</v>
       </c>
     </row>
   </sheetData>
